--- a/erp-server/erp-server-file/src/main/resources/excel/wms/requisitionApplicationChangeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/requisitionApplicationChangeExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>变更单号</t>
   </si>
@@ -47,6 +47,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>三方仓</t>
     </r>
     <r>
@@ -61,6 +69,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>平台产品</t>
     </r>
     <r>
@@ -75,6 +91,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>平台</t>
     </r>
     <r>
@@ -158,6 +182,9 @@
   </si>
   <si>
     <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.approveUserName}</t>
   </si>
   <si>
     <t>{.createTime}</t>
@@ -1912,13 +1939,13 @@
         <v>31</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
